--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260816_200913.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260816_200913.xlsx
@@ -6488,7 +6488,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260816_200913.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260816_200913.xlsx
@@ -6488,7 +6488,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
